--- a/supplementary-material/Supplementary Table S19.xlsx
+++ b/supplementary-material/Supplementary Table S19.xlsx
@@ -4,9 +4,7 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/huhuiling/AI_Employment/4 paper：VR WCE/Supplement827/"/>
-    </mc:Choice>
+    <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B93D0D6-3E89-0D4D-9EB4-F3AF924E726B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
@@ -1761,9 +1759,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="ChatGPT">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1813,7 +1811,7 @@
         <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="ChatGPT">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
